--- a/AtchisonRegime/Outputs/Aust/ASX300_Materials/df_regSummary_ASX300_Materials.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Materials/df_regSummary_ASX300_Materials.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>1.631953697597222</v>
+        <v>1.615308826197647</v>
       </c>
       <c r="H2" t="n">
-        <v>5.007471232994456</v>
+        <v>4.986514646365134</v>
       </c>
       <c r="I2" t="n">
         <v>-10.9393768664177</v>
@@ -545,19 +545,19 @@
         <v>14.5795620340833</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L2" t="n">
         <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1508575647433518</v>
+        <v>0.1507567468514205</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.08626110315509194</v>
+        <v>-0.08747091785826677</v>
       </c>
       <c r="P2" t="n">
         <v>0.4668459700393814</v>
@@ -603,7 +603,7 @@
         <v>10.463139776602</v>
       </c>
       <c r="K3" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L3" t="n">
         <v>12</v>
@@ -661,7 +661,7 @@
         <v>11.502191267126</v>
       </c>
       <c r="K4" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>16.133821600917</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L5" t="n">
         <v>12</v>
